--- a/web/files/九龙-红磡-必嘉坊．迎汇.xlsx
+++ b/web/files/九龙-红磡-必嘉坊．迎汇.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2023-03-06</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2023-02-05</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2022-12-13</t>
+          <t>2022-12-14</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
+          <t>2022-12-09</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-05-15</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-03-31</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-02</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17428,7 +17428,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18362,7 +18362,7 @@
           <t>E | 270呎 (1房)
 $513万
 $19,011/呎
-(25年-03月-06日)</t>
+(25年-03月-07日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -18370,7 +18370,7 @@
           <t>F | 270呎 (1房)
 $659万
 $24,400/呎
-(26年-06月-24日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -18387,7 +18387,7 @@
           <t>J | 400呎 (2房)
 $1186万
 $29,639/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -18395,7 +18395,7 @@
           <t>K | 377呎 (1房)
 $1021万
 $27,072/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr">
@@ -18403,7 +18403,7 @@
           <t>L | 214呎 (开放式)
 $578万
 $27,000/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -18434,7 +18434,7 @@
           <t>A | 223呎 (开放式)
 $431万
 $19,336/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -18442,7 +18442,7 @@
           <t>B | 378呎 (2房)
 $936万
 $24,760/呎
-(23年-02月-06日)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -18450,7 +18450,7 @@
           <t>C | 514呎 (3房)
 $1126万
 $21,898/呎
-(23年-05月-07日)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
           <t>E | 270呎 (1房)
 $546万
 $20,210/呎
-(23年-05月-15日)</t>
+(23年-05月-16日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -18467,7 +18467,7 @@
           <t>F | 270呎 (1房)
 $598万
 $22,134/呎
-(23年-06月-14日)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -18475,7 +18475,7 @@
           <t>G | 271呎 (1房)
 $549万
 $20,242/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr"/>
@@ -18484,7 +18484,7 @@
           <t>J | 508呎 (3房)
 $1049万
 $20,644/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -18492,7 +18492,7 @@
           <t>K | 374呎 (1房)
 $811万
 $21,672/呎
-(23年-05月-21日)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -18500,7 +18500,7 @@
           <t>L | 214呎 (开放式)
 $451万
 $21,070/呎
-(23年-06月-15日)</t>
+(23年-06月-16日)</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
@@ -18508,7 +18508,7 @@
           <t>M | 214呎 (开放式)
 $416万
 $19,438/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="N6" s="22" t="inlineStr">
@@ -18516,7 +18516,7 @@
           <t>N | 324呎 (1房)
 $650万
 $20,056/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -18531,7 +18531,7 @@
           <t>A | 223呎 (开放式)
 $430万
 $19,276/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -18539,7 +18539,7 @@
           <t>B | 378呎 (2房)
 $848万
 $22,445/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -18547,7 +18547,7 @@
           <t>C | 515呎 (3房)
 $1209万
 $23,483/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr"/>
@@ -18556,7 +18556,7 @@
           <t>E | 270呎 (1房)
 $544万
 $20,153/呎
-(23年-05月-08日)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -18564,7 +18564,7 @@
           <t>F | 270呎 (1房)
 $556万
 $20,583/呎
-(23年-07月-03日)</t>
+(23年-07月-04日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -18572,7 +18572,7 @@
           <t>G | 271呎 (1房)
 $590万
 $21,755/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr"/>
@@ -18581,7 +18581,7 @@
           <t>J | 508呎 (3房)
 $1125万
 $22,144/呎
-(24年-04月-11日)</t>
+(24年-04月-12日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -18589,7 +18589,7 @@
           <t>K | 374呎 (1房)
 $867万
 $23,170/呎
-(23年-06月-19日)</t>
+(23年-06月-20日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -18597,7 +18597,7 @@
           <t>L | 214呎 (开放式)
 $450万
 $21,020/呎
-(23年-05月-30日)</t>
+(23年-05月-31日)</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -18605,7 +18605,7 @@
           <t>M | 214呎 (开放式)
 $415万
 $19,383/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="N7" s="22" t="inlineStr">
@@ -18613,7 +18613,7 @@
           <t>N | 324呎 (1房)
 $641万
 $19,778/呎
-(23年-05月-17日)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
           <t>A | 223呎 (开放式)
 $429万
 $19,223/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -18636,7 +18636,7 @@
           <t>B | 378呎 (2房)
 $814万
 $21,548/呎
-(24年-01月-16日)</t>
+(24年-01月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -18644,7 +18644,7 @@
           <t>C | 278呎 (1房)
 $589万
 $21,202/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -18652,7 +18652,7 @@
           <t>D | 273呎 (1房)
 $552万
 $20,205/呎
-(23年-05月-15日)</t>
+(23年-05月-16日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -18660,7 +18660,7 @@
           <t>E | 270呎 (1房)
 $585万
 $21,656/呎
-(23年-05月-21日)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -18668,7 +18668,7 @@
           <t>F | 270呎 (1房)
 $554万
 $20,527/呎
-(23年-07月-12日)</t>
+(23年-07月-13日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -18676,7 +18676,7 @@
           <t>G | 270呎 (1房)
 $600万
 $22,220/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -18684,7 +18684,7 @@
           <t>H | 270呎 (1房)
 $538万
 $19,917/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -18692,7 +18692,7 @@
           <t>J | 276呎 (1房)
 $558万
 $20,204/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -18700,7 +18700,7 @@
           <t>K | 374呎 (1房)
 $787万
 $21,030/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -18708,7 +18708,7 @@
           <t>L | 214呎 (开放式)
 $418万
 $19,511/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
@@ -18716,7 +18716,7 @@
           <t>M | 214呎 (开放式)
 $414万
 $19,324/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="N8" s="22" t="inlineStr">
@@ -18724,7 +18724,7 @@
           <t>N | 324呎 (1房)
 $617万
 $19,047/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18739,7 @@
           <t>A | 223呎 (开放式)
 $427万
 $19,167/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -18747,7 +18747,7 @@
           <t>B | 378呎 (2房)
 $812万
 $21,486/呎
-(23年-07月-03日)</t>
+(23年-07月-04日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -18755,7 +18755,7 @@
           <t>C | 278呎 (1房)
 $588万
 $21,140/呎
-(23年-05月-29日)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -18763,7 +18763,7 @@
           <t>D | 274呎 (1房)
 $550万
 $20,073/呎
-(23年-05月-29日)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -18771,7 +18771,7 @@
           <t>E | 270呎 (1房)
 $541万
 $20,033/呎
-(23年-05月-21日)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -18779,7 +18779,7 @@
           <t>F | 270呎 (1房)
 $592万
 $21,941/呎
-(23年-07月-19日)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -18787,7 +18787,7 @@
           <t>G | 270呎 (1房)
 $583万
 $21,594/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -18795,7 +18795,7 @@
           <t>H | 270呎 (1房)
 $536万
 $19,860/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -18803,7 +18803,7 @@
           <t>J | 276呎 (1房)
 $556万
 $20,146/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -18811,7 +18811,7 @@
           <t>K | 374呎 (1房)
 $784万
 $20,970/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -18819,7 +18819,7 @@
           <t>L | 214呎 (开放式)
 $416万
 $19,452/呎
-(25年-06月-02日)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -18827,7 +18827,7 @@
           <t>M | 214呎 (开放式)
 $412万
 $19,265/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="N9" s="22" t="inlineStr">
@@ -18835,7 +18835,7 @@
           <t>N | 324呎 (1房)
 $677万
 $20,888/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -18850,7 +18850,7 @@
           <t>A | 223呎 (开放式)
 $426万
 $19,111/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -18858,7 +18858,7 @@
           <t>B | 378呎 (2房)
 $810万
 $21,421/呎
-(24年-03月-21日)</t>
+(24年-03月-22日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -18866,7 +18866,7 @@
           <t>C | 278呎 (1房)
 $586万
 $21,076/呎
-(23年-05月-24日)</t>
+(23年-05月-25日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -18874,7 +18874,7 @@
           <t>D | 274呎 (1房)
 $548万
 $20,014/呎
-(23年-05月-22日)</t>
+(23年-05月-23日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -18882,7 +18882,7 @@
           <t>E | 270呎 (1房)
 $539万
 $19,973/呎
-(23年-05月-07日)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -18890,7 +18890,7 @@
           <t>F | 270呎 (1房)
 $606万
 $22,443/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -18898,7 +18898,7 @@
           <t>G | 270呎 (1房)
 $542万
 $20,083/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -18906,7 +18906,7 @@
           <t>H | 270呎 (1房)
 $573万
 $21,233/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -18914,7 +18914,7 @@
           <t>J | 276呎 (1房)
 $532万
 $19,272/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -18922,7 +18922,7 @@
           <t>K | 374呎 (1房)
 $791万
 $21,139/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -18930,7 +18930,7 @@
           <t>L | 214呎 (开放式)
 $415万
 $19,397/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
@@ -18938,7 +18938,7 @@
           <t>M | 214呎 (开放式)
 $411万
 $19,210/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="N10" s="22" t="inlineStr">
@@ -18946,7 +18946,7 @@
           <t>N | 324呎 (1房)
 $613万
 $18,906/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18961,7 @@
           <t>A | 223呎 (开放式)
 $425万
 $19,058/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -18969,7 +18969,7 @@
           <t>B | 378呎 (2房)
 $807万
 $21,360/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -18977,7 +18977,7 @@
           <t>C | 278呎 (1房)
 $584万
 $21,014/呎
-(23年-07月-27日)</t>
+(23年-07月-28日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -18985,7 +18985,7 @@
           <t>D | 274呎 (1房)
 $589万
 $21,510/呎
-(23年-05月-10日)</t>
+(23年-05月-11日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>E | 270呎 (1房)
 $544万
 $20,138/呎
-(23年-05月-17日)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -19001,7 +19001,7 @@
           <t>F | 270呎 (1房)
 $592万
 $21,929/呎
-(23年-07月-24日)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -19009,7 +19009,7 @@
           <t>G | 270呎 (1房)
 $541万
 $20,023/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -19017,7 +19017,7 @@
           <t>H | 270呎 (1房)
 $533万
 $19,747/呎
-(23年-04月-20日)</t>
+(23年-04月-21日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -19025,7 +19025,7 @@
           <t>J | 276呎 (1房)
 $553万
 $20,028/呎
-(23年-04月-17日)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -19033,7 +19033,7 @@
           <t>K | 374呎 (1房)
 $780万
 $20,847/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -19041,7 +19041,7 @@
           <t>L | 214呎 (开放式)
 $427万
 $19,964/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -19049,7 +19049,7 @@
           <t>M | 214呎 (开放式)
 $410万
 $19,151/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="N11" s="22" t="inlineStr">
@@ -19057,7 +19057,7 @@
           <t>N | 324呎 (1房)
 $654万
 $20,181/呎
-(23年-04月-17日)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
           <t>A | 223呎 (开放式)
 $424万
 $19,002/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -19080,7 +19080,7 @@
           <t>B | 378呎 (2房)
 $805万
 $21,295/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -19088,7 +19088,7 @@
           <t>C | 278呎 (1房)
 $656万
 $23,583/呎
-(23年-03月-22日)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -19096,7 +19096,7 @@
           <t>D | 274呎 (1房)
 $585万
 $21,335/呎
-(23年-05月-17日)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -19104,7 +19104,7 @@
           <t>E | 270呎 (1房)
 $575万
 $21,291/呎
-(23年-05月-11日)</t>
+(23年-05月-12日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19112,7 +19112,7 @@
           <t>F | 270呎 (1房)
 $587万
 $21,748/呎
-(23年-07月-24日)</t>
+(23年-07月-25日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -19120,7 +19120,7 @@
           <t>G | 270呎 (1房)
 $539万
 $19,963/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -19128,7 +19128,7 @@
           <t>H | 270呎 (1房)
 $532万
 $19,687/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -19136,7 +19136,7 @@
           <t>J | 276呎 (1房)
 $591万
 $21,412/呎
-(23年-04月-16日)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -19144,7 +19144,7 @@
           <t>K | 374呎 (1房)
 $834万
 $22,288/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -19152,7 +19152,7 @@
           <t>L | 214呎 (开放式)
 $426万
 $19,905/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -19160,7 +19160,7 @@
           <t>M | 214呎 (开放式)
 $414万
 $19,340/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="N12" s="22" t="inlineStr">
@@ -19168,7 +19168,7 @@
           <t>N | 324呎 (1房)
 $613万
 $18,919/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19183,7 +19183,7 @@
           <t>A | 223呎 (开放式)
 $423万
 $18,949/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19191,7 +19191,7 @@
           <t>B | 378呎 (2房)
 $803万
 $21,233/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -19199,7 +19199,7 @@
           <t>C | 278呎 (1房)
 $579万
 $20,839/呎
-(23年-08月-29日)</t>
+(23年-08月-30日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -19207,7 +19207,7 @@
           <t>D | 273呎 (1房)
 $562万
 $20,576/呎
-(23年-05月-23日)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -19215,7 +19215,7 @@
           <t>E | 270呎 (1房)
 $540万
 $20,016/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -19223,7 +19223,7 @@
           <t>F | 270呎 (1房)
 $546万
 $20,223/呎
-(23年-07月-13日)</t>
+(23年-07月-14日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -19231,7 +19231,7 @@
           <t>G | 270呎 (1房)
 $537万
 $19,907/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -19239,7 +19239,7 @@
           <t>H | 270呎 (1房)
 $568万
 $21,047/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -19247,7 +19247,7 @@
           <t>J | 276呎 (1房)
 $592万
 $21,459/呎
-(23年-04月-20日)</t>
+(23年-04月-21日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -19255,7 +19255,7 @@
           <t>K | 374呎 (1房)
 $775万
 $20,724/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -19263,7 +19263,7 @@
           <t>L | 214呎 (开放式)
 $455万
 $21,279/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -19271,7 +19271,7 @@
           <t>M | 214呎 (开放式)
 $446万
 $20,830/呎
-(23年-07月-30日)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="N13" s="22" t="inlineStr">
@@ -19279,7 +19279,7 @@
           <t>N | 324呎 (1房)
 $648万
 $20,003/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
           <t>A | 223呎 (开放式)
 $421万
 $18,889/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19302,7 +19302,7 @@
           <t>B | 378呎 (2房)
 $798万
 $21,107/呎
-(24年-05月-08日)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19310,7 +19310,7 @@
           <t>C | 278呎 (1房)
 $652万
 $23,442/呎
-(23年-03月-06日)</t>
+(23年-03月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19318,7 +19318,7 @@
           <t>D | 274呎 (1房)
 $542万
 $19,784/呎
-(23年-05月-21日)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -19326,7 +19326,7 @@
           <t>E | 270呎 (1房)
 $533万
 $19,740/呎
-(23年-05月-14日)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -19334,7 +19334,7 @@
           <t>F | 270呎 (1房)
 $584万
 $21,619/呎
-(23年-07月-23日)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -19342,7 +19342,7 @@
           <t>G | 270呎 (1房)
 $542万
 $20,067/呎
-(23年-05月-07日)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -19350,7 +19350,7 @@
           <t>H | 270呎 (1房)
 $570万
 $21,096/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -19358,7 +19358,7 @@
           <t>J | 276呎 (1房)
 $587万
 $21,286/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -19366,7 +19366,7 @@
           <t>K | 374呎 (1房)
 $849万
 $22,701/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -19374,7 +19374,7 @@
           <t>L | 214呎 (开放式)
 $428万
 $20,007/呎
-(23年-05月-09日)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
@@ -19382,7 +19382,7 @@
           <t>M | 214呎 (开放式)
 $395万
 $18,480/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="N14" s="22" t="inlineStr">
@@ -19390,7 +19390,7 @@
           <t>N | 324呎 (1房)
 $646万
 $19,943/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19405,7 @@
           <t>A | 223呎 (开放式)
 $420万
 $18,836/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19413,7 +19413,7 @@
           <t>B | 378呎 (2房)
 $811万
 $21,467/呎
-(24年-06月-23日)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -19421,7 +19421,7 @@
           <t>C | 278呎 (1房)
 $650万
 $23,375/呎
-(23年-02月-05日)</t>
+(23年-02月-06日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -19429,7 +19429,7 @@
           <t>D | 274呎 (1房)
 $540万
 $19,724/呎
-(23年-05月-14日)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -19437,7 +19437,7 @@
           <t>E | 270呎 (1房)
 $570万
 $21,101/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19445,7 +19445,7 @@
           <t>F | 270呎 (1房)
 $543万
 $20,103/呎
-(23年-07月-03日)</t>
+(23年-07月-04日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>G | 270呎 (1房)
 $534万
 $19,787/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -19461,7 +19461,7 @@
           <t>H | 270呎 (1房)
 $527万
 $19,517/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -19469,7 +19469,7 @@
           <t>J | 276呎 (1房)
 $546万
 $19,793/呎
-(23年-04月-20日)</t>
+(23年-04月-21日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -19477,7 +19477,7 @@
           <t>K | 374呎 (1房)
 $789万
 $21,109/呎
-(23年-05月-15日)</t>
+(23年-05月-16日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -19485,7 +19485,7 @@
           <t>L | 214呎 (开放式)
 $464万
 $21,701/呎
-(23年-05月-09日)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -19493,7 +19493,7 @@
           <t>M | 214呎 (开放式)
 $394万
 $18,421/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -19501,7 +19501,7 @@
           <t>N | 324呎 (1房)
 $648万
 $19,987/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
           <t>A | 222呎 (开放式)
 $471万
 $21,223/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19524,7 +19524,7 @@
           <t>B | 378呎 (2房)
 $793万
 $20,981/呎
-(24年-04月-07日)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -19532,7 +19532,7 @@
           <t>C | 278呎 (1房)
 $574万
 $20,655/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -19540,7 +19540,7 @@
           <t>D | 274呎 (1房)
 $539万
 $19,665/呎
-(23年-05月-23日)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -19548,7 +19548,7 @@
           <t>E | 270呎 (1房)
 $571万
 $21,146/呎
-(23年-05月-08日)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -19556,7 +19556,7 @@
           <t>F | 270呎 (1房)
 $541万
 $20,043/呎
-(23年-07月-19日)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -19564,7 +19564,7 @@
           <t>G | 270呎 (1房)
 $571万
 $21,155/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -19572,7 +19572,7 @@
           <t>H | 270呎 (1房)
 $563万
 $20,862/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -19580,7 +19580,7 @@
           <t>J | 276呎 (1房)
 $587万
 $21,270/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -19588,7 +19588,7 @@
           <t>K | 374呎 (1房)
 $782万
 $20,913/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -19596,7 +19596,7 @@
           <t>L | 214呎 (开放式)
 $421万
 $19,670/呎
-(23年-05月-22日)</t>
+(23年-05月-23日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -19604,7 +19604,7 @@
           <t>M | 214呎 (开放式)
 $393万
 $18,366/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -19612,7 +19612,7 @@
           <t>N | 324呎 (1房)
 $599万
 $18,489/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
           <t>A | 222呎 (开放式)
 $470万
 $21,158/呎
-(23年-04月-10日)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>B | 378呎 (2房)
 $791万
 $20,919/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>C | 278呎 (1房)
 $572万
 $20,590/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -19651,7 +19651,7 @@
           <t>D | 274呎 (1房)
 $537万
 $19,609/呎
-(23年-05月-23日)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -19659,7 +19659,7 @@
           <t>E | 270呎 (1房)
 $546万
 $20,215/呎
-(23年-05月-09日)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -19667,7 +19667,7 @@
           <t>F | 270呎 (1房)
 $540万
 $19,983/呎
-(23年-07月-10日)</t>
+(23年-07月-11日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -19675,7 +19675,7 @@
           <t>G | 270呎 (1房)
 $531万
 $19,670/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -19683,7 +19683,7 @@
           <t>H | 270呎 (1房)
 $565万
 $20,909/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -19691,7 +19691,7 @@
           <t>J | 276呎 (1房)
 $585万
 $21,206/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -19699,7 +19699,7 @@
           <t>K | 374呎 (1房)
 $761万
 $20,341/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -19707,7 +19707,7 @@
           <t>L | 214呎 (开放式)
 $423万
 $19,769/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -19715,7 +19715,7 @@
           <t>M | 214呎 (开放式)
 $409万
 $19,128/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -19723,7 +19723,7 @@
           <t>N | 324呎 (1房)
 $597万
 $18,433/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
           <t>A | 222呎 (开放式)
 $468万
 $21,097/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -19746,7 +19746,7 @@
           <t>B | 378呎 (2房)
 $818万
 $21,631/呎
-(24年-06月-18日)</t>
+(24年-06月-19日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -19754,7 +19754,7 @@
           <t>C | 278呎 (1房)
 $571万
 $20,528/呎
-(24年-03月-25日)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -19762,7 +19762,7 @@
           <t>D | 274呎 (1房)
 $536万
 $19,550/呎
-(23年-05月-21日)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -19770,7 +19770,7 @@
           <t>E | 270呎 (1房)
 $565万
 $20,912/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -19778,7 +19778,7 @@
           <t>F | 270呎 (1房)
 $538万
 $19,923/呎
-(23年-06月-26日)</t>
+(23年-06月-27日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -19786,7 +19786,7 @@
           <t>G | 270呎 (1房)
 $568万
 $21,026/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -19794,7 +19794,7 @@
           <t>H | 270呎 (1房)
 $560万
 $20,740/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -19802,7 +19802,7 @@
           <t>J | 276呎 (1房)
 $541万
 $19,617/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -19810,7 +19810,7 @@
           <t>K | 374呎 (1房)
 $770万
 $20,602/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -19818,7 +19818,7 @@
           <t>L | 214呎 (开放式)
 $445万
 $20,774/呎
-(23年-06月-01日)</t>
+(23年-06月-02日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -19826,7 +19826,7 @@
           <t>M | 214呎 (开放式)
 $391万
 $18,257/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -19834,7 +19834,7 @@
           <t>N | 324呎 (1房)
 $642万
 $19,807/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
           <t>A | 222呎 (开放式)
 $467万
 $21,032/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -19857,7 +19857,7 @@
           <t>B | 378呎 (2房)
 $758万
 $20,040/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -19865,7 +19865,7 @@
           <t>C | 278呎 (1房)
 $569万
 $20,467/呎
-(23年-09月-11日)</t>
+(23年-09月-12日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -19873,7 +19873,7 @@
           <t>D | 273呎 (1房)
 $534万
 $19,563/呎
-(23年-05月-17日)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -19881,7 +19881,7 @@
           <t>E | 270呎 (1房)
 $525万
 $19,443/呎
-(23年-05月-14日)</t>
+(23年-05月-15日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -19889,7 +19889,7 @@
           <t>F | 270呎 (1房)
 $575万
 $21,298/呎
-(23年-07月-05日)</t>
+(23年-07月-06日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -19897,7 +19897,7 @@
           <t>G | 270呎 (1房)
 $528万
 $19,553/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -19905,7 +19905,7 @@
           <t>H | 270呎 (1房)
 $538万
 $19,929/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -19913,7 +19913,7 @@
           <t>J | 276呎 (1房)
 $540万
 $19,559/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -19921,7 +19921,7 @@
           <t>K | 374呎 (1房)
 $741万
 $19,817/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -19929,7 +19929,7 @@
           <t>L | 214呎 (开放式)
 $412万
 $19,257/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -19937,7 +19937,7 @@
           <t>M | 214呎 (开放式)
 $438万
 $20,456/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -19945,7 +19945,7 @@
           <t>N | 324呎 (1房)
 $600万
 $18,526/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -19960,7 +19960,7 @@
           <t>A | 222呎 (开放式)
 $466万
 $20,972/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>B | 378呎 (2房)
 $784万
 $20,729/呎
-(24年-04月-25日)</t>
+(24年-04月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>C | 278呎 (1房)
 $588万
 $21,147/呎
-(22年-12月-13日)</t>
+(22年-12月-14日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -19984,7 +19984,7 @@
           <t>D | 274呎 (1房)
 $533万
 $19,435/呎
-(23年-05月-16日)</t>
+(23年-05月-17日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -19992,7 +19992,7 @@
           <t>E | 270呎 (1房)
 $541万
 $20,033/呎
-(23年-05月-07日)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -20000,7 +20000,7 @@
           <t>F | 270呎 (1房)
 $535万
 $19,803/呎
-(23年-07月-11日)</t>
+(23年-07月-12日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -20008,7 +20008,7 @@
           <t>G | 270呎 (1房)
 $564万
 $20,901/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -20016,7 +20016,7 @@
           <t>H | 270呎 (1房)
 $519万
 $19,227/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -20024,7 +20024,7 @@
           <t>J | 276呎 (1房)
 $577万
 $20,908/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -20032,7 +20032,7 @@
           <t>K | 374呎 (1房)
 $792万
 $21,183/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -20040,7 +20040,7 @@
           <t>L | 214呎 (开放式)
 $411万
 $19,199/呎
-(23年-05月-23日)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -20048,7 +20048,7 @@
           <t>M | 214呎 (开放式)
 $388万
 $18,146/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -20056,7 +20056,7 @@
           <t>N | 324呎 (1房)
 $612万
 $18,875/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20071,7 @@
           <t>A | 223呎 (开放式)
 $418万
 $18,755/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>B | 378呎 (2房)
 $814万
 $21,529/呎
-(22年-12月-08日)</t>
+(22年-12月-09日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20087,7 +20087,7 @@
           <t>C | 278呎 (1房)
 $566万
 $20,344/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20095,7 +20095,7 @@
           <t>D | 273呎 (1房)
 $531万
 $19,447/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -20103,7 +20103,7 @@
           <t>E | 270呎 (1房)
 $574万
 $21,259/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -20111,7 +20111,7 @@
           <t>F | 270呎 (1房)
 $571万
 $21,166/呎
-(23年-06月-22日)</t>
+(23年-06月-23日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -20119,7 +20119,7 @@
           <t>G | 270呎 (1房)
 $563万
 $20,837/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -20127,7 +20127,7 @@
           <t>H | 270呎 (1房)
 $518万
 $19,170/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -20135,7 +20135,7 @@
           <t>J | 276呎 (1房)
 $575万
 $20,845/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -20143,7 +20143,7 @@
           <t>K | 374呎 (1房)
 $766万
 $20,483/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -20151,7 +20151,7 @@
           <t>L | 214呎 (开放式)
 $438万
 $20,477/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -20159,7 +20159,7 @@
           <t>M | 214呎 (开放式)
 $387万
 $18,092/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -20167,7 +20167,7 @@
           <t>N | 324呎 (1房)
 $631万
 $19,467/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20182,7 @@
           <t>A | 223呎 (开放式)
 $412万
 $18,463/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20190,7 +20190,7 @@
           <t>B | 378呎 (2房)
 $746万
 $19,728/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20198,7 +20198,7 @@
           <t>C | 278呎 (1房)
 $583万
 $20,958/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20206,7 +20206,7 @@
           <t>D | 273呎 (1房)
 $568万
 $20,788/呎
-(23年-05月-17日)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -20214,121 +20214,10 @@
           <t>E | 270呎 (1房)
 $558万
 $20,658/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>F | 270呎 (1房)
-$531万
-$19,683/呎
-(23年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>G | 270呎 (1房)
-$541万
-$20,022/呎
-(23年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>H | 270呎 (1房)
-$553万
-$20,494/呎
-(23年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>J | 276呎 (1房)
-$577万
-$20,890/呎
-(23年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
-        <is>
-          <t>K | 374呎 (1房)
-$745万
-$19,930/呎
-(23年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="inlineStr">
-        <is>
-          <t>L | 214呎 (开放式)
-$436万
-$20,369/呎
-(23年-04月-25日)</t>
-        </is>
-      </c>
-      <c r="M22" s="22" t="inlineStr">
-        <is>
-          <t>M | 214呎 (开放式)
-$434万
-$20,271/呎
-(23年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="N22" s="22" t="inlineStr">
-        <is>
-          <t>N | 324呎 (1房)
-$585万
-$18,056/呎
-(23年-04月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>A | 223呎 (开放式)
-$412万
-$18,463/呎
-(25年-11月-02日)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>B | 378呎 (2房)
-$714万
-$18,885/呎
-(25年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>C | 278呎 (1房)
-$591万
-$21,251/呎
-(23年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>D | 273呎 (1房)
-$568万
-$20,788/呎
-(23年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>E | 270呎 (1房)
-$538万
-$19,909/呎
-(23年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
 $531万
@@ -20336,12 +20225,123 @@
 (23年-06月-15日)</t>
         </is>
       </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 270呎 (1房)
+$541万
+$20,022/呎
+(23年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 270呎 (1房)
+$553万
+$20,494/呎
+(23年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 276呎 (1房)
+$577万
+$20,890/呎
+(23年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 374呎 (1房)
+$745万
+$19,930/呎
+(23年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>L | 214呎 (开放式)
+$436万
+$20,369/呎
+(23年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>M | 214呎 (开放式)
+$434万
+$20,271/呎
+(23年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>N | 324呎 (1房)
+$585万
+$18,056/呎
+(23年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 223呎 (开放式)
+$412万
+$18,463/呎
+(25年-11月-03日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (2房)
+$714万
+$18,885/呎
+(25年-02月-14日)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 278呎 (1房)
+$591万
+$21,251/呎
+(23年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 273呎 (1房)
+$568万
+$20,788/呎
+(23年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 270呎 (1房)
+$538万
+$19,909/呎
+(23年-05月-09日)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 270呎 (1房)
+$531万
+$19,683/呎
+(23年-06月-16日)</t>
+        </is>
+      </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 270呎 (1房)
 $523万
 $19,377/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -20349,7 +20349,7 @@
           <t>H | 270呎 (1房)
 $562万
 $20,812/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -20357,7 +20357,7 @@
           <t>J | 276呎 (1房)
 $577万
 $20,890/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -20365,7 +20365,7 @@
           <t>K | 374呎 (1房)
 $745万
 $19,930/呎
-(23年-05月-01日)</t>
+(23年-05月-02日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -20373,7 +20373,7 @@
           <t>L | 214呎 (开放式)
 $406万
 $18,955/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -20381,7 +20381,7 @@
           <t>M | 214呎 (开放式)
 $394万
 $18,389/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -20389,7 +20389,7 @@
           <t>N | 324呎 (1房)
 $590万
 $18,197/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -20404,7 +20404,7 @@
           <t>A | 222呎 (开放式)
 $461万
 $20,785/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -20412,7 +20412,7 @@
           <t>B | 378呎 (2房)
 $777万
 $20,543/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -20420,7 +20420,7 @@
           <t>C | 278呎 (1房)
 $562万
 $20,218/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -20428,7 +20428,7 @@
           <t>D | 274呎 (1房)
 $528万
 $19,261/呎
-(23年-05月-21日)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -20436,7 +20436,7 @@
           <t>E | 270呎 (1房)
 $556万
 $20,597/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -20444,7 +20444,7 @@
           <t>F | 270呎 (1房)
 $547万
 $20,277/呎
-(23年-06月-07日)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -20452,7 +20452,7 @@
           <t>G | 270呎 (1房)
 $522万
 $19,317/呎
-(23年-05月-09日)</t>
+(23年-05月-10日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -20460,7 +20460,7 @@
           <t>H | 270呎 (1房)
 $552万
 $20,429/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -20468,7 +20468,7 @@
           <t>J | 276呎 (1房)
 $533万
 $19,324/呎
-(23年-04月-24日)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -20476,7 +20476,7 @@
           <t>K | 374呎 (1房)
 $767万
 $20,520/呎
-(23年-05月-04日)</t>
+(23年-05月-05日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -20484,7 +20484,7 @@
           <t>L | 214呎 (开放式)
 $433万
 $20,215/呎
-(23年-05月-24日)</t>
+(23年-05月-25日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -20492,7 +20492,7 @@
           <t>M | 214呎 (开放式)
 $464万
 $21,667/呎
-(23年-06月-28日)</t>
+(23年-06月-29日)</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
@@ -20500,7 +20500,7 @@
           <t>N | 324呎 (1房)
 $581万
 $17,944/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20515,7 @@
           <t>A | 222呎 (开放式)
 $500万
 $22,505/呎
-(22年-12月-01日)</t>
+(22年-12月-02日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -20523,7 +20523,7 @@
           <t>B | 378呎 (2房)
 $772万
 $20,417/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -20531,7 +20531,7 @@
           <t>C | 278呎 (1房)
 $560万
 $20,156/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -20539,7 +20539,7 @@
           <t>D | 274呎 (1房)
 $564万
 $20,599/呎
-(23年-05月-15日)</t>
+(23年-05月-16日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -20547,7 +20547,7 @@
           <t>E | 270呎 (1房)
 $554万
 $20,504/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -20555,7 +20555,7 @@
           <t>F | 270呎 (1房)
 $528万
 $19,553/呎
-(23年-06月-08日)</t>
+(23年-06月-09日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -20563,7 +20563,7 @@
           <t>G | 270呎 (1房)
 $520万
 $19,257/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -20571,7 +20571,7 @@
           <t>H | 270呎 (1房)
 $513万
 $18,993/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -20579,7 +20579,7 @@
           <t>J | 276呎 (1房)
 $532万
 $19,265/呎
-(23年-04月-18日)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -20587,7 +20587,7 @@
           <t>K | 374呎 (1房)
 $739万
 $19,747/呎
-(23年-05月-02日)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -20595,7 +20595,7 @@
           <t>L | 214呎 (开放式)
 $400万
 $18,681/呎
-(23年-04月-27日)</t>
+(23年-04月-28日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -20603,7 +20603,7 @@
           <t>M | 214呎 (开放式)
 $399万
 $18,630/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -20611,7 +20611,7 @@
           <t>N | 324呎 (1房)
 $580万
 $17,908/呎
-(23年-04月-20日)</t>
+(23年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -20626,7 +20626,7 @@
           <t>A | 201呎 (开放式)
 $408万
 $20,289/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -20642,7 +20642,7 @@
           <t>C | 240呎 (1房)
 $715万
 $29,800/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -20650,7 +20650,7 @@
           <t>D | 236呎 (1房)
 $565万
 $23,943/呎
-(23年-05月-24日)</t>
+(23年-05月-25日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -20658,7 +20658,7 @@
           <t>E | 233呎 (1房)
 $551万
 $23,661/呎
-(23年-05月-28日)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -20666,7 +20666,7 @@
           <t>F | 232呎 (1房)
 $559万
 $24,110/呎
-(24年-06月-13日)</t>
+(24年-06月-14日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -20674,7 +20674,7 @@
           <t>G | 232呎 (1房)
 $554万
 $23,895/呎
-(23年-06月-26日)</t>
+(23年-06月-27日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -20682,7 +20682,7 @@
           <t>H | 233呎 (1房)
 $545万
 $23,381/呎
-(23年-07月-26日)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -20690,7 +20690,7 @@
           <t>J | 238呎 (1房)
 $615万
 $25,832/呎
-(23年-07月-03日)</t>
+(23年-07月-04日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -20698,7 +20698,7 @@
           <t>K | 336呎 (1房)
 $666万
 $19,819/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -20706,7 +20706,7 @@
           <t>L | 193呎 (开放式)
 $388万
 $20,113/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -20714,7 +20714,7 @@
           <t>M | 193呎 (开放式)
 $392万
 $20,300/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -20722,7 +20722,7 @@
           <t>N | 286呎 (1房)
 $602万
 $21,037/呎
-(23年-07月-26日)</t>
+(23年-07月-27日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-红磡-必嘉坊．迎汇.xlsx
+++ b/web/files/九龙-红磡-必嘉坊．迎汇.xlsx
@@ -4098,14 +4098,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>5924100</v>
+        <v>5520000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>21941</v>
+        <v>20444</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>5924100</v>
+        <v>5520000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>21941</v>
+        <v>20444</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -18777,9 +18777,9 @@
       <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 270呎 (1房)
-$592万
-$21,941/呎
-(23年-07月-20日)</t>
+$552万
+$20,444/呎
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
